--- a/keyref2_log_training_excel/training_keyref2.xlsx
+++ b/keyref2_log_training_excel/training_keyref2.xlsx
@@ -437,1507 +437,1507 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-30</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-22</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-18</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-26</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-28</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>-26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -1947,3677 +1947,3677 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>-20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-22</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>-26</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>-28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-28</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>-28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>-26</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>-26</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>-16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>-24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>-26</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>-28</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>-28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>-24</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>-24</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>-26</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>-28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>-28</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>-26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>-26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>-28</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>-28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>-26</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>-18</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>-24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>-22</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>-22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>-22</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>-20</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>-24</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>-26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>-24</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>-26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>-28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>-28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>-26</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>-28</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>-28</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>-28</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>-26</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>-18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>-26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>-24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>-24</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>-28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>-28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>-18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>-18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>-16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>-24</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>-24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>-18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>-28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>-24</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>-24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>-28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>-28</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>-24</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>-16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>-24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>-28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1039">
@@ -5627,1482 +5627,1482 @@
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>-26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>-18</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>-22</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>-20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>-20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>-20</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>-20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>-24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>-24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>-30</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/keyref2_log_training_excel/training_keyref2.xlsx
+++ b/keyref2_log_training_excel/training_keyref2.xlsx
@@ -437,52 +437,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -492,37 +492,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -532,52 +532,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -587,27 +587,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -617,22 +617,22 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="42">
@@ -642,12 +642,12 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="45">
@@ -657,147 +657,147 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-19</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="75">
@@ -812,252 +812,252 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>7</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="127">
@@ -1067,167 +1067,167 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -1237,12 +1237,12 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -1252,22 +1252,22 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -1277,42 +1277,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="178">
@@ -1322,22 +1322,22 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="183">
@@ -1347,142 +1347,142 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="212">
@@ -1492,82 +1492,82 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="229">
@@ -1577,37 +1577,37 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="237">
@@ -1617,12 +1617,12 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="240">
@@ -1632,42 +1632,42 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -1677,22 +1677,22 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="254">
@@ -1702,272 +1702,272 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>7</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="309">
@@ -1977,167 +1977,167 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="343">
@@ -2147,57 +2147,57 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>2</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="355">
@@ -2207,12 +2207,12 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="358">
@@ -2222,27 +2222,27 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="364">
@@ -2252,22 +2252,22 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="369">
@@ -2282,37 +2282,37 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="378">
@@ -2322,107 +2322,107 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>-8</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="400">
@@ -2432,112 +2432,112 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -2547,12 +2547,12 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="426">
@@ -2562,47 +2562,47 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="436">
@@ -2612,52 +2612,52 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="447">
@@ -2667,52 +2667,52 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -2722,82 +2722,82 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="475">
@@ -2807,22 +2807,22 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="480">
@@ -2832,32 +2832,32 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
@@ -2867,67 +2867,67 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -2937,47 +2937,47 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>-26</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="511">
@@ -2992,87 +2992,87 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="530">
@@ -3082,12 +3082,12 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="533">
@@ -3097,202 +3097,202 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="574">
@@ -3302,52 +3302,52 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="585">
@@ -3357,47 +3357,47 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="595">
@@ -3407,17 +3407,17 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="599">
@@ -3427,57 +3427,57 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="611">
@@ -3487,227 +3487,227 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>-7</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="657">
@@ -3717,17 +3717,17 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661">
@@ -3737,242 +3737,242 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>10</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="710">
@@ -3982,162 +3982,162 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="743">
@@ -4147,102 +4147,102 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="764">
@@ -4252,52 +4252,52 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>-6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="775">
@@ -4307,157 +4307,157 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>1</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>-2</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="807">
@@ -4467,22 +4467,22 @@
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="812">
@@ -4492,27 +4492,27 @@
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="818">
@@ -4522,22 +4522,22 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="823">
@@ -4547,47 +4547,47 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="833">
@@ -4597,37 +4597,37 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>-5</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="841">
@@ -4637,27 +4637,27 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="847">
@@ -4667,77 +4667,77 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="863">
@@ -4752,37 +4752,37 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="872">
@@ -4792,197 +4792,197 @@
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="912">
@@ -4992,7 +4992,7 @@
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="914">
@@ -5007,7 +5007,7 @@
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="917">
@@ -5017,62 +5017,62 @@
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="930">
@@ -5082,82 +5082,82 @@
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="947">
@@ -5167,17 +5167,17 @@
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="951">
@@ -5187,47 +5187,47 @@
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="961">
@@ -5237,27 +5237,27 @@
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="967">
@@ -5272,142 +5272,142 @@
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-2</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="997">
@@ -5417,147 +5417,147 @@
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1027">
@@ -5567,147 +5567,147 @@
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1057">
@@ -5717,12 +5717,12 @@
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1060">
@@ -5737,22 +5737,22 @@
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1066">
@@ -5762,47 +5762,47 @@
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1076">
@@ -5812,22 +5812,22 @@
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1081">
@@ -5837,87 +5837,87 @@
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>-5</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1099">
@@ -5927,62 +5927,62 @@
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1112">
@@ -5992,52 +5992,52 @@
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1123">
@@ -6047,27 +6047,27 @@
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1129">
@@ -6077,42 +6077,42 @@
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1138">
@@ -6122,137 +6122,137 @@
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1166">
@@ -6262,222 +6262,222 @@
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1211">
@@ -6487,392 +6487,392 @@
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>-13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>8</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1290">
@@ -6882,57 +6882,57 @@
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1302">
@@ -6942,52 +6942,52 @@
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1313">
@@ -6997,112 +6997,112 @@
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>-2</v>
+        <v>-15</v>
       </c>
     </row>
   </sheetData>

--- a/keyref2_log_training_excel/training_keyref2.xlsx
+++ b/keyref2_log_training_excel/training_keyref2.xlsx
@@ -437,482 +437,482 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-23</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-13</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -922,192 +922,192 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -1117,62 +1117,62 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="150">
@@ -1182,77 +1182,77 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="166">
@@ -1262,77 +1262,77 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="182">
@@ -1342,122 +1342,122 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-3</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="207">
@@ -1472,87 +1472,87 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="226">
@@ -1562,12 +1562,12 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="229">
@@ -1577,12 +1577,12 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="232">
@@ -1592,7 +1592,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="234">
@@ -1602,82 +1602,82 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="251">
@@ -1687,147 +1687,147 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="281">
@@ -1837,82 +1837,82 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="298">
@@ -1922,52 +1922,52 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="309">
@@ -1977,42 +1977,42 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="318">
@@ -2022,62 +2022,62 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="331">
@@ -2087,7 +2087,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="333">
@@ -2097,32 +2097,32 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="340">
@@ -2132,312 +2132,312 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>-21</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>-17</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="403">
@@ -2447,52 +2447,52 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="414">
@@ -2502,157 +2502,157 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>-4</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -2662,12 +2662,12 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="449">
@@ -2677,67 +2677,67 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>-20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="463">
@@ -2752,12 +2752,12 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="467">
@@ -2767,7 +2767,7 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="469">
@@ -2777,62 +2777,62 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="482">
@@ -2842,52 +2842,52 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="493">
@@ -2897,42 +2897,42 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -2942,167 +2942,167 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="536">
@@ -3112,27 +3112,27 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="542">
@@ -3142,82 +3142,82 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -3227,112 +3227,112 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
@@ -3342,12 +3342,12 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="585">
@@ -3357,112 +3357,112 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="608">
@@ -3472,7 +3472,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="610">
@@ -3482,67 +3482,67 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="624">
@@ -3552,67 +3552,67 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="638">
@@ -3622,17 +3622,17 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="642">
@@ -3642,87 +3642,87 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="660">
@@ -3732,17 +3732,17 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="664">
@@ -3752,37 +3752,37 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
@@ -3792,12 +3792,12 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="675">
@@ -3807,27 +3807,27 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="681">
@@ -3837,32 +3837,32 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="688">
@@ -3872,102 +3872,102 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="709">
@@ -3977,157 +3977,157 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
@@ -4137,92 +4137,92 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="760">
@@ -4232,32 +4232,32 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="767">
@@ -4267,7 +4267,7 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="769">
@@ -4277,67 +4277,67 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="783">
@@ -4347,42 +4347,42 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="792">
@@ -4392,52 +4392,52 @@
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="803">
@@ -4447,32 +4447,32 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="810">
@@ -4482,132 +4482,132 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>1</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="837">
@@ -4617,172 +4617,172 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>-16</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="872">
@@ -4792,42 +4792,42 @@
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="881">
@@ -4837,192 +4837,192 @@
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>15</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="920">
@@ -5032,152 +5032,152 @@
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="951">
@@ -5187,47 +5187,47 @@
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="961">
@@ -5237,372 +5237,372 @@
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>-1</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1036">
@@ -5617,112 +5617,112 @@
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1060">
@@ -5732,77 +5732,77 @@
     </row>
     <row r="1061">
       <c r="A1061" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1076">
@@ -5812,32 +5812,32 @@
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1083">
@@ -5847,77 +5847,77 @@
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1099">
@@ -5927,27 +5927,27 @@
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1105">
@@ -5957,417 +5957,417 @@
     </row>
     <row r="1106">
       <c r="A1106" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1189">
@@ -6377,22 +6377,22 @@
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>-12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1194">
@@ -6402,52 +6402,52 @@
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1205">
@@ -6457,122 +6457,122 @@
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="1230">
@@ -6582,32 +6582,32 @@
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1237">
@@ -6617,67 +6617,67 @@
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1251">
@@ -6692,137 +6692,137 @@
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1280">
@@ -6832,7 +6832,7 @@
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1282">
@@ -6842,132 +6842,132 @@
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1309">
@@ -6982,72 +6982,72 @@
     </row>
     <row r="1311">
       <c r="A1311" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1325">
@@ -7057,22 +7057,22 @@
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1330">
@@ -7082,27 +7082,27 @@
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>

--- a/keyref2_log_training_excel/training_keyref2.xlsx
+++ b/keyref2_log_training_excel/training_keyref2.xlsx
@@ -437,427 +437,427 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-9</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-17</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -867,57 +867,57 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -927,157 +927,157 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>3</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="131">
@@ -1087,77 +1087,77 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1167,1102 +1167,1102 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>-8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>-7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>-9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>-8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-5</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>-16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-7</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>-11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>3</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>5</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="368">
@@ -2272,307 +2272,307 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>-4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -2582,722 +2582,722 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-2</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>2</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-4</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>-4</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-9</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>-6</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-2</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-2</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>-3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>-6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-6</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>-3</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>-7</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-6</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>2</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>-2</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>-1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-1</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>-1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>-3</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>-6</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>-4</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>2</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>-1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>-1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>-7</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>-2</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>-5</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>-9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>-7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>-6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>-4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>-2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="575">
@@ -3312,287 +3312,287 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -3607,17 +3607,17 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="639">
@@ -3627,67 +3627,67 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653">
@@ -3697,12 +3697,12 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -3712,17 +3712,17 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -3732,862 +3732,862 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>-4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>1</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="833">
@@ -4602,227 +4602,227 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>-13</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>-3</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>-6</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>1</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="880">
@@ -4832,7 +4832,7 @@
     </row>
     <row r="881">
       <c r="A881" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="882">
@@ -4842,767 +4842,767 @@
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>-4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>-8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>-6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>-6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>-8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>-4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>-5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>-8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>-7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>-6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>-8</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>-9</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>-3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>-8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>2</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>-6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>-4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>-3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>-5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>-6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>-2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1036">
@@ -5612,947 +5612,947 @@
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>-6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>-8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>-3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>-4</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>-4</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>4</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>-4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>4</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>-16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>-12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>-10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>-7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>-9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>-7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>-5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>-9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>-8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1226">
@@ -6562,182 +6562,182 @@
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1263">
@@ -6747,142 +6747,142 @@
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1292">
@@ -6892,217 +6892,217 @@
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>-9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
   </sheetData>

--- a/keyref2_log_training_excel/training_keyref2.xlsx
+++ b/keyref2_log_training_excel/training_keyref2.xlsx
@@ -557,57 +557,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="37">
@@ -622,7 +622,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -637,77 +637,77 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-21</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -792,72 +792,72 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -867,7 +867,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -877,17 +877,17 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -897,7 +897,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -907,332 +907,332 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-30</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="162">
@@ -1342,92 +1342,92 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>11</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -1442,482 +1442,482 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>-15</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-27</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>6</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="299">
@@ -1927,117 +1927,117 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -2047,52 +2047,52 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334">
@@ -2102,7 +2102,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336">
@@ -2112,12 +2112,12 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339">
@@ -2127,7 +2127,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341">
@@ -2137,7 +2137,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343">
@@ -2147,22 +2147,22 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
@@ -2172,37 +2172,37 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>-27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="356">
@@ -2262,72 +2262,72 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>-18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>16</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="381">
@@ -2352,142 +2352,142 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>-30</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="413">
@@ -2517,77 +2517,77 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="433">
@@ -2597,7 +2597,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="435">
@@ -2607,22 +2607,22 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>-14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="440">
@@ -2632,57 +2632,57 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="452">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>-18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="458">
@@ -2747,132 +2747,132 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>-18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="490">
@@ -2892,17 +2892,17 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="496">
@@ -2942,17 +2942,17 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="506">
@@ -2962,17 +2962,17 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="510">
@@ -2982,7 +2982,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="512">
@@ -3007,12 +3007,12 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="518">
@@ -3027,302 +3027,302 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>-14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>-30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>-30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>-10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>-30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>-30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>-14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>-30</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="580">
@@ -3477,32 +3477,32 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>-30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="616">
@@ -3522,57 +3522,57 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="630">
@@ -3592,297 +3592,297 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="692">
@@ -3932,7 +3932,7 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>-30</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="702">
@@ -3942,12 +3942,12 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="705">
@@ -3957,7 +3957,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="707">
@@ -3977,302 +3977,302 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>-8</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>-8</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>-6</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>-9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>-30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>-30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>-30</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="770">
@@ -4347,77 +4347,77 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>17</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>16</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="799">
@@ -4442,147 +4442,147 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>-27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>-30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>-30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>-30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>-30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>-30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>-30</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="832">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="837">
@@ -4637,27 +4637,27 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>-26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>-21</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="847">
@@ -4777,47 +4777,47 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>-30</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="879">
@@ -4847,17 +4847,17 @@
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="887">
@@ -4867,52 +4867,52 @@
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>24</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="898">
@@ -4957,77 +4957,77 @@
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="921">
@@ -5037,72 +5037,72 @@
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>-2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="936">
@@ -5122,17 +5122,17 @@
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="942">
@@ -5257,167 +5257,167 @@
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="n">
-        <v>-30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="n">
-        <v>-30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
-        <v>-30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="n">
-        <v>-14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>-30</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="999">
@@ -5502,22 +5502,22 @@
     </row>
     <row r="1015">
       <c r="A1015" t="n">
-        <v>-16</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>-14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1019">
@@ -5532,112 +5532,112 @@
     </row>
     <row r="1021">
       <c r="A1021" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
-        <v>22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
-        <v>24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
-        <v>22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
-        <v>-21</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1043">
@@ -5692,27 +5692,27 @@
     </row>
     <row r="1053">
       <c r="A1053" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
-        <v>-30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1058">
@@ -5737,47 +5737,47 @@
     </row>
     <row r="1062">
       <c r="A1062" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>-14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1071">
@@ -5792,167 +5792,167 @@
     </row>
     <row r="1073">
       <c r="A1073" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
-        <v>-30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="n">
-        <v>-30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>-30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>-30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="1106">
@@ -6007,57 +6007,57 @@
     </row>
     <row r="1116">
       <c r="A1116" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
-        <v>22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
-        <v>24</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="n">
-        <v>28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
-        <v>22</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="n">
-        <v>-12</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1127">
@@ -6082,12 +6082,12 @@
     </row>
     <row r="1131">
       <c r="A1131" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1133">
@@ -6117,122 +6117,122 @@
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>18</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>28</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>28</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>20</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>-30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>-30</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1162">
@@ -6242,217 +6242,217 @@
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>4</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>9</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>21</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>8</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>-8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>-30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>-30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1206">
@@ -6492,452 +6492,452 @@
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>2</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>1</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>5</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>5</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>5</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>5</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="1303">
@@ -6997,112 +6997,112 @@
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>-30</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
